--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13243" uniqueCount="2631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13251" uniqueCount="2633">
   <si>
     <t>Result</t>
   </si>
@@ -7964,6 +7964,12 @@
   </si>
   <si>
     <t>Mon Nov 17 04:27:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 19:58:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 20:00:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -20672,10 +20678,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>2589</v>
+        <v>2631</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -20754,10 +20760,10 @@
     </row>
     <row ht="72" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>2590</v>
+        <v>2632</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>

--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7683" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8851" uniqueCount="1533">
   <si>
     <t>Result</t>
   </si>
@@ -3794,6 +3794,882 @@
   </si>
   <si>
     <t>Tue Mar 10 23:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:51:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:53:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:55:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:56:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:56:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:57:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:58:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 16:59:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:00:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:01:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:02:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:04:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:06:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:24:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:25:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:26:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:27:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:28:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:28:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:29:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:30:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:32:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:33:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:34:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:35:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:39:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:41:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:42:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:43:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:46:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:47:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:48:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:50:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:51:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:52:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:53:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:54:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:55:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:56:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:57:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:58:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 17:59:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:00:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:01:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:02:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:03:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:05:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:07:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:08:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:09:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:09:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:10:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:11:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:12:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:15:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:16:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:17:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:18:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:19:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:19:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 18:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:19:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:21:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:23:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:24:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:25:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:25:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:27:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:28:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:29:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:30:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:33:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:34:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:35:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:36:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:37:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:38:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:39:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:41:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:42:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:43:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:43:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:45:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:46:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:48:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:49:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:50:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:51:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:52:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:56:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:57:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 23:58:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:00:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:01:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:02:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:03:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:04:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:05:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:07:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:08:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:11:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:12:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:15:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:15:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:16:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:17:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:19:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:20:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:21:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:21:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:22:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:23:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:24:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:25:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:28:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:30:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:30:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:31:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:32:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:34:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:35:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:50:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:51:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:52:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:53:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:54:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 00:55:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:13:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:14:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:15:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:16:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:17:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 01:59:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:00:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:02:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:03:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:03:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:05:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:06:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:08:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:09:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:10:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:11:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:12:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:13:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:14:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:14:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:17:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:18:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:19:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:20:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:21:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:22:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:23:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:24:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:25:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:26:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:26:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:29:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:30:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:31:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:32:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:33:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:34:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 02:35:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:32:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 21:36:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:34:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:39:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:40:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:41:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:42:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:43:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:44:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:46:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:47:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:49:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:50:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:51:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:52:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:53:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:54:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:56:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:58:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 22:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:01:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:03:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:05:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:09:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:10:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:11:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:13:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:14:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:16:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:18:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:19:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:20:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:21:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:22:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:23:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:24:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:25:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:27:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:28:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:29:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:30:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:31:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:34:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:36:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:38:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:40:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:42:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:43:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:44:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:46:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:48:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:49:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:50:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:51:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:53:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu May 07 23:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 19:34:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 19:35:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 19:37:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 08 19:38:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -4325,7 +5201,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1111</v>
+        <v>1519</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -4363,7 +5239,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1112</v>
+        <v>1520</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -4443,7 +5319,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1113</v>
+        <v>1521</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -4523,7 +5399,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1114</v>
+        <v>1522</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>37</v>
@@ -4591,7 +5467,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1115</v>
+        <v>1523</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -4629,7 +5505,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1116</v>
+        <v>1524</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -4709,7 +5585,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>1117</v>
+        <v>1525</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -4789,7 +5665,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>1118</v>
+        <v>1526</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>37</v>
@@ -4957,7 +5833,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1135</v>
+        <v>1391</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -5041,7 +5917,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1136</v>
+        <v>1392</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -5221,7 +6097,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1143</v>
+        <v>1399</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -5303,7 +6179,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1144</v>
+        <v>1400</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -5484,7 +6360,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1139</v>
+        <v>1395</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -5568,7 +6444,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1140</v>
+        <v>1396</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -5751,7 +6627,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1147</v>
+        <v>1403</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -5835,7 +6711,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1404</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -6015,7 +6891,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1209</v>
+        <v>1479</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -6096,7 +6972,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1210</v>
+        <v>1480</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -6149,7 +7025,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1211</v>
+        <v>1481</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -6230,7 +7106,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1212</v>
+        <v>1482</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -6384,7 +7260,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1223</v>
+        <v>1487</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -6438,7 +7314,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1224</v>
+        <v>1488</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -6520,7 +7396,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1225</v>
+        <v>1489</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -6574,7 +7450,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1226</v>
+        <v>1490</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -6758,7 +7634,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1231</v>
+        <v>1501</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -6845,7 +7721,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1232</v>
+        <v>1502</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -6906,7 +7782,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1233</v>
+        <v>1503</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -6993,7 +7869,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1234</v>
+        <v>1504</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -7156,7 +8032,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1235</v>
+        <v>1509</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -7240,10 +8116,10 @@
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1236</v>
+        <v>1510</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -7304,7 +8180,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1237</v>
+        <v>1511</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -7391,7 +8267,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1238</v>
+        <v>1512</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -7548,7 +8424,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1219</v>
+        <v>1483</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7602,7 +8478,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1220</v>
+        <v>1484</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -7684,7 +8560,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1221</v>
+        <v>1485</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -7738,7 +8614,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1222</v>
+        <v>1486</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -7916,7 +8792,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1205</v>
+        <v>1469</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -7997,7 +8873,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1206</v>
+        <v>1470</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -8050,7 +8926,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1207</v>
+        <v>1471</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -8131,7 +9007,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1208</v>
+        <v>1472</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -8310,7 +9186,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1193</v>
+        <v>1491</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -8393,7 +9269,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1194</v>
+        <v>1492</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -8431,7 +9307,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1195</v>
+        <v>1493</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -8502,7 +9378,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1196</v>
+        <v>1494</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -8585,7 +9461,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1197</v>
+        <v>1495</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -8623,7 +9499,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1198</v>
+        <v>1496</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -8797,7 +9673,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1239</v>
+        <v>1505</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -8881,10 +9757,10 @@
     </row>
     <row ht="86.4" r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1240</v>
+        <v>1506</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -8945,7 +9821,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1229</v>
+        <v>1507</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -9032,7 +9908,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1230</v>
+        <v>1508</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -9562,7 +10438,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1155</v>
+        <v>1411</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -9644,7 +10520,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1156</v>
+        <v>1412</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -9822,7 +10698,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1157</v>
+        <v>1413</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -9903,7 +10779,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1158</v>
+        <v>1414</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -10094,7 +10970,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1159</v>
+        <v>1415</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -10184,7 +11060,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1160</v>
+        <v>1416</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -10370,7 +11246,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1161</v>
+        <v>1417</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -10460,7 +11336,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1162</v>
+        <v>1418</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -10646,7 +11522,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1167</v>
+        <v>1423</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -10736,7 +11612,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1168</v>
+        <v>1424</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -10917,7 +11793,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1163</v>
+        <v>1419</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -10999,7 +11875,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1164</v>
+        <v>1420</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11176,7 +12052,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1165</v>
+        <v>1421</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11257,7 +12133,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1166</v>
+        <v>1422</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11448,7 +12324,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1169</v>
+        <v>1425</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11538,7 +12414,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1170</v>
+        <v>1426</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11740,7 +12616,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1199</v>
+        <v>1513</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -11823,7 +12699,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1200</v>
+        <v>1514</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -11861,7 +12737,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1201</v>
+        <v>1515</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -11932,7 +12808,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1202</v>
+        <v>1516</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -12015,7 +12891,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1203</v>
+        <v>1517</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -12053,7 +12929,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1204</v>
+        <v>1518</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -12221,7 +13097,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1123</v>
+        <v>1529</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -12277,7 +13153,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1124</v>
+        <v>1530</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -12333,7 +13209,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1125</v>
+        <v>1531</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -12389,7 +13265,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1126</v>
+        <v>1532</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -12550,7 +13426,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1127</v>
+        <v>1461</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12616,7 +13492,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1128</v>
+        <v>1462</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -12682,7 +13558,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1129</v>
+        <v>1463</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -12748,7 +13624,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1130</v>
+        <v>1464</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -12919,7 +13795,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1131</v>
+        <v>1465</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12985,7 +13861,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1132</v>
+        <v>1466</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -13051,7 +13927,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1133</v>
+        <v>1467</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -13117,7 +13993,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1134</v>
+        <v>1468</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -13276,10 +14152,10 @@
     </row>
     <row ht="43.2" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1119</v>
+        <v>1453</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -13333,10 +14209,10 @@
     </row>
     <row ht="43.2" r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1120</v>
+        <v>1454</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -13393,7 +14269,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1121</v>
+        <v>1455</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>68</v>
@@ -13450,7 +14326,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1122</v>
+        <v>1456</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -13605,10 +14481,10 @@
     </row>
     <row ht="72" r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1187</v>
+        <v>1443</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -13659,7 +14535,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1188</v>
+        <v>1444</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -13815,7 +14691,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1189</v>
+        <v>1445</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -13875,7 +14751,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1190</v>
+        <v>1446</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14040,7 +14916,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1191</v>
+        <v>1447</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -14100,7 +14976,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1192</v>
+        <v>1448</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14256,7 +15132,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1185</v>
+        <v>1441</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -14306,7 +15182,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1186</v>
+        <v>1442</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -14454,7 +15330,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1173</v>
+        <v>1429</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -14514,7 +15390,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1174</v>
+        <v>1430</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -14681,7 +15557,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1177</v>
+        <v>1433</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -14747,7 +15623,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1178</v>
+        <v>1434</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -14934,7 +15810,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1213</v>
+        <v>1473</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15014,7 +15890,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1214</v>
+        <v>1474</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15052,7 +15928,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1215</v>
+        <v>1475</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>69</v>
@@ -15117,7 +15993,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1216</v>
+        <v>1476</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -15197,7 +16073,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1217</v>
+        <v>1477</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>68</v>
@@ -15235,7 +16111,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1218</v>
+        <v>1478</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>69</v>
@@ -15397,7 +16273,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1175</v>
+        <v>1431</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15454,7 +16330,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1176</v>
+        <v>1432</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -15621,7 +16497,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1179</v>
+        <v>1435</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15687,7 +16563,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1180</v>
+        <v>1436</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -15858,7 +16734,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1184</v>
+        <v>1440</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16029,7 +16905,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1183</v>
+        <v>1439</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16191,7 +17067,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1181</v>
+        <v>1437</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -16347,7 +17223,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1182</v>
+        <v>1438</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16505,7 +17381,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1151</v>
+        <v>1407</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -16587,7 +17463,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1152</v>
+        <v>1408</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -16768,7 +17644,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1153</v>
+        <v>1527</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -16850,7 +17726,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1154</v>
+        <v>1528</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -17029,7 +17905,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1171</v>
+        <v>1427</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -17082,7 +17958,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1172</v>
+        <v>1428</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -17236,7 +18112,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1137</v>
+        <v>1393</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -17307,7 +18183,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1138</v>
+        <v>1394</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -17474,7 +18350,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1145</v>
+        <v>1401</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -17545,7 +18421,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1146</v>
+        <v>1402</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -17715,7 +18591,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1141</v>
+        <v>1397</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -17799,7 +18675,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1142</v>
+        <v>1398</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -17982,7 +18858,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1149</v>
+        <v>1405</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -18066,7 +18942,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1150</v>
+        <v>1406</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>

--- a/KatalonData/IWPTestData/VRelay25Payments.xlsx
+++ b/KatalonData/IWPTestData/VRelay25Payments.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8851" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9739" uniqueCount="1755">
   <si>
     <t>Result</t>
   </si>
@@ -4670,6 +4670,672 @@
   </si>
   <si>
     <t>Fri May 08 19:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:52:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:53:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:54:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:55:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:56:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:57:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:58:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 22:59:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:01:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:02:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:02:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:03:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:04:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:06:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:07:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:08:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:10:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:11:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:12:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:13:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:15:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:17:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:18:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:19:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:20:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:21:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:22:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:23:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:25:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:26:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:27:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:28:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:30:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:33:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:35:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:36:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:37:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:38:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:39:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:40:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:42:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:45:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:46:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:46:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:47:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:48:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:49:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:50:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:51:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:52:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:56:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:56:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:57:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:58:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 23:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:00:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:01:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:03:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:03:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:04:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:14:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:15:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:16:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:17:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:18:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:19:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:20:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:21:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:35:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:36:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:37:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:39:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:40:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:41:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 00:42:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:18:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:20:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:21:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:22:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:23:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:24:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:25:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:26:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:27:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:28:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:29:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:30:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:32:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:33:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:34:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:34:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:35:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:37:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:37:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:38:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:39:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:40:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:40:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:41:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:43:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:45:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:46:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:47:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:48:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:49:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:50:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:51:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 01:52:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:40:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 19:42:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:31:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:32:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:33:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:35:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:36:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:37:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:38:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:38:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:39:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:41:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:43:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:47:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:48:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:49:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:52:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:54:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:55:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:56:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:57:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:58:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:59:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:00:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:02:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:03:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:07:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:08:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:10:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:11:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:12:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:13:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:14:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:15:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:16:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:17:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:22:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:23:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:24:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:25:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:26:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:27:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:28:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:29:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:32:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:33:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:34:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:35:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:35:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:37:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:38:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:41:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:42:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:42:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:43:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:44:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:45:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 22:46:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 20:53:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 20:55:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 20:56:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 09 20:57:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 10 20:06:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 10 20:07:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 10 20:08:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 10 20:09:53 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -5201,7 +5867,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1519</v>
+        <v>1737</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -5239,7 +5905,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1520</v>
+        <v>1738</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -5319,7 +5985,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1521</v>
+        <v>1739</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -5399,7 +6065,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1522</v>
+        <v>1740</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>37</v>
@@ -5467,7 +6133,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1523</v>
+        <v>1741</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -5505,7 +6171,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1524</v>
+        <v>1742</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -5585,7 +6251,7 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>1525</v>
+        <v>1743</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -5665,7 +6331,7 @@
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>1526</v>
+        <v>1744</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>37</v>
@@ -5833,7 +6499,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1391</v>
+        <v>1607</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -5917,7 +6583,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1392</v>
+        <v>1608</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -6097,7 +6763,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1399</v>
+        <v>1615</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -6179,7 +6845,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1400</v>
+        <v>1616</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -6360,7 +7026,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1395</v>
+        <v>1611</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -6444,7 +7110,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1396</v>
+        <v>1612</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -6627,7 +7293,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1403</v>
+        <v>1619</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -6711,7 +7377,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1404</v>
+        <v>1620</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -6891,7 +7557,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1479</v>
+        <v>1697</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -6972,7 +7638,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1480</v>
+        <v>1698</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -7025,7 +7691,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1481</v>
+        <v>1699</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -7106,7 +7772,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1482</v>
+        <v>1700</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -7260,7 +7926,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1487</v>
+        <v>1705</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -7314,7 +7980,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1488</v>
+        <v>1706</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -7396,7 +8062,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1489</v>
+        <v>1707</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -7450,7 +8116,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1490</v>
+        <v>1708</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -7634,7 +8300,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1501</v>
+        <v>1719</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -7721,7 +8387,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1502</v>
+        <v>1720</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -7782,7 +8448,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1503</v>
+        <v>1721</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -7869,7 +8535,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1504</v>
+        <v>1722</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -8032,7 +8698,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1509</v>
+        <v>1727</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -8119,7 +8785,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1510</v>
+        <v>1728</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -8180,7 +8846,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1511</v>
+        <v>1729</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -8267,7 +8933,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1512</v>
+        <v>1730</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -8424,7 +9090,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1483</v>
+        <v>1701</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -8478,7 +9144,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1484</v>
+        <v>1702</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -8560,7 +9226,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1485</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -8614,7 +9280,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1486</v>
+        <v>1704</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -8792,7 +9458,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1469</v>
+        <v>1687</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -8873,7 +9539,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1470</v>
+        <v>1688</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -8926,7 +9592,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1471</v>
+        <v>1689</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -9007,7 +9673,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1472</v>
+        <v>1690</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -9186,7 +9852,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1491</v>
+        <v>1709</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -9269,7 +9935,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1492</v>
+        <v>1710</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -9307,7 +9973,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1493</v>
+        <v>1711</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -9378,7 +10044,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1494</v>
+        <v>1712</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -9461,7 +10127,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1495</v>
+        <v>1713</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -9499,7 +10165,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1496</v>
+        <v>1714</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -9673,7 +10339,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1505</v>
+        <v>1723</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>82</v>
@@ -9760,7 +10426,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1506</v>
+        <v>1724</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>83</v>
@@ -9821,7 +10487,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1507</v>
+        <v>1725</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>82</v>
@@ -9908,7 +10574,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1508</v>
+        <v>1726</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>83</v>
@@ -10438,7 +11104,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1411</v>
+        <v>1627</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -10520,7 +11186,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1412</v>
+        <v>1628</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -10698,7 +11364,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1413</v>
+        <v>1629</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -10779,7 +11445,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1414</v>
+        <v>1630</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -10970,7 +11636,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1415</v>
+        <v>1631</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11060,7 +11726,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1416</v>
+        <v>1632</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11246,7 +11912,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1417</v>
+        <v>1633</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11336,7 +12002,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1418</v>
+        <v>1634</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11522,7 +12188,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1423</v>
+        <v>1639</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -11612,7 +12278,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1424</v>
+        <v>1640</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -11793,7 +12459,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1419</v>
+        <v>1635</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -11875,7 +12541,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1420</v>
+        <v>1636</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12052,7 +12718,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1421</v>
+        <v>1637</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12133,7 +12799,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1422</v>
+        <v>1638</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12324,7 +12990,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1425</v>
+        <v>1641</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -12414,7 +13080,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1426</v>
+        <v>1642</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -12616,7 +13282,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1513</v>
+        <v>1731</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -12699,7 +13365,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1514</v>
+        <v>1732</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>61</v>
@@ -12737,7 +13403,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1515</v>
+        <v>1733</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>62</v>
@@ -12808,7 +13474,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1516</v>
+        <v>1734</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -12891,7 +13557,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1517</v>
+        <v>1735</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>61</v>
@@ -12929,7 +13595,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1518</v>
+        <v>1736</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>62</v>
@@ -13097,7 +13763,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1529</v>
+        <v>1751</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -13153,7 +13819,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1530</v>
+        <v>1752</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -13209,7 +13875,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1531</v>
+        <v>1753</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -13265,7 +13931,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1532</v>
+        <v>1754</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -13426,7 +14092,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1461</v>
+        <v>1679</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -13492,7 +14158,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1462</v>
+        <v>1680</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -13558,7 +14224,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1463</v>
+        <v>1681</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -13624,7 +14290,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1464</v>
+        <v>1682</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -13795,7 +14461,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1465</v>
+        <v>1683</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -13861,7 +14527,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1466</v>
+        <v>1684</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -13927,7 +14593,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1467</v>
+        <v>1685</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>66</v>
@@ -13993,7 +14659,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1468</v>
+        <v>1686</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -14155,7 +14821,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1453</v>
+        <v>1671</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -14212,7 +14878,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1454</v>
+        <v>1672</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14269,7 +14935,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1455</v>
+        <v>1673</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>68</v>
@@ -14326,7 +14992,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1456</v>
+        <v>1674</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>68</v>
@@ -14484,7 +15150,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1443</v>
+        <v>1659</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -14535,7 +15201,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1444</v>
+        <v>1660</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14691,7 +15357,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1445</v>
+        <v>1661</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -14751,7 +15417,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1446</v>
+        <v>1662</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -14916,7 +15582,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1447</v>
+        <v>1663</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -14976,7 +15642,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1448</v>
+        <v>1664</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15132,7 +15798,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1441</v>
+        <v>1657</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -15182,7 +15848,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1442</v>
+        <v>1658</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -15330,7 +15996,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1429</v>
+        <v>1645</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -15390,7 +16056,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1430</v>
+        <v>1646</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -15557,7 +16223,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1433</v>
+        <v>1649</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15623,7 +16289,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1434</v>
+        <v>1650</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -15810,7 +16476,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1473</v>
+        <v>1691</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -15890,7 +16556,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1474</v>
+        <v>1692</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -15928,7 +16594,7 @@
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>1475</v>
+        <v>1693</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>69</v>
@@ -15993,7 +16659,7 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>1476</v>
+        <v>1694</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -16073,7 +16739,7 @@
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>1477</v>
+        <v>1695</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>68</v>
@@ -16111,7 +16777,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>1478</v>
+        <v>1696</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>69</v>
@@ -16273,7 +16939,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1431</v>
+        <v>1647</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16330,7 +16996,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1432</v>
+        <v>1648</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -16497,7 +17163,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1435</v>
+        <v>1651</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16563,7 +17229,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1436</v>
+        <v>1652</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>66</v>
@@ -16734,7 +17400,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1440</v>
+        <v>1656</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -16905,7 +17571,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1439</v>
+        <v>1655</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17067,7 +17733,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1437</v>
+        <v>1653</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -17223,7 +17889,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1438</v>
+        <v>1654</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>66</v>
@@ -17381,7 +18047,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1407</v>
+        <v>1623</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -17463,7 +18129,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1408</v>
+        <v>1624</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -17644,7 +18310,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1527</v>
+        <v>1745</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -17726,7 +18392,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1528</v>
+        <v>1746</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -17905,7 +18571,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1427</v>
+        <v>1643</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>68</v>
@@ -17958,7 +18624,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1428</v>
+        <v>1644</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
@@ -18112,7 +18778,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1393</v>
+        <v>1609</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -18183,7 +18849,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1394</v>
+        <v>1610</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -18350,7 +19016,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1401</v>
+        <v>1617</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>69</v>
@@ -18421,7 +19087,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1402</v>
+        <v>1618</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>69</v>
@@ -18591,7 +19257,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1397</v>
+        <v>1613</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -18675,7 +19341,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1398</v>
+        <v>1614</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
@@ -18858,7 +19524,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>1405</v>
+        <v>1621</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>59</v>
@@ -18942,7 +19608,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>1406</v>
+        <v>1622</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
